--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalChargesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file INTEGRATED BILLING ACTION (350) to Invoice</t>
+    <t>This StructureDefinition contains the maps for VistA file INTEGRATED BILLING ACTION (350) to Invoice.</t>
   </si>
   <si>
     <t>Purpose</t>
